--- a/Data/students_COMPS.xlsx
+++ b/Data/students_COMPS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repositories\kjsitfeedback\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C28771C-0647-4326-878D-1C23470BE372}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3CB9E6E-EB69-4E41-ADF7-D5218F1B11B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3380" uniqueCount="1518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3380" uniqueCount="1519">
   <si>
     <t>First Name</t>
   </si>
@@ -4586,13 +4586,16 @@
   </si>
   <si>
     <t>7COMPSB73</t>
+  </si>
+  <si>
+    <t>shaunak.gite@somaiya.edu</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4605,6 +4608,14 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -4645,17 +4656,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -9609,11 +9623,11 @@
       <c r="B161" t="s">
         <v>672</v>
       </c>
-      <c r="C161" t="s">
-        <v>569</v>
-      </c>
-      <c r="D161" t="s">
-        <v>569</v>
+      <c r="C161" s="3" t="s">
+        <v>1518</v>
+      </c>
+      <c r="D161" s="3" t="s">
+        <v>1518</v>
       </c>
       <c r="E161" t="s">
         <v>673</v>
@@ -17172,6 +17186,10 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C161" r:id="rId1" xr:uid="{CC0EE3D6-1CE3-427E-BAEF-9477F9382E13}"/>
+    <hyperlink ref="D161" r:id="rId2" xr:uid="{9D6289B5-BDF1-4D23-9621-6794BA999EB0}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
